--- a/ig/specifications_techniques/StructureDefinition-dui-documentreference.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-dui-documentreference.xlsx
@@ -9,11 +9,14 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$55</definedName>
+  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1791" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2187" uniqueCount="450">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-12T14:26:59+00:00</t>
+    <t>2023-09-13T08:02:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +75,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profil générique créé dans le contexte du transfert de données DUI pour véhiculer le dossier au format CDA.</t>
+    <t>Profil générique créé dans le contexte du transfert de données DUI pour véhiculer le dossier au format CDA, inclus dans DocumentReference.attachment.data.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -911,7 +914,7 @@
     <t>DocumentReference.content</t>
   </si>
   <si>
-    <t>Document referenced</t>
+    <t>Document contenu.</t>
   </si>
   <si>
     <t>The document and format referenced. There may be multiple content element repetitions, each with a different format.</t>
@@ -964,6 +967,211 @@
   </si>
   <si>
     <t>DocumentEntry.mimeType, DocumentEntry.languageCode, DocumentEntry.URI, DocumentEntry.size, DocumentEntry.hash, DocumentEntry.title, DocumentEntry.creationTime</t>
+  </si>
+  <si>
+    <t>DocumentReference.content.attachment.id</t>
+  </si>
+  <si>
+    <t>DocumentReference.content.attachment.extension</t>
+  </si>
+  <si>
+    <t>DocumentReference.content.attachment.contentType</t>
+  </si>
+  <si>
+    <t>Mime type of the content, with charset etc.</t>
+  </si>
+  <si>
+    <t>Identifies the type of the data in the attachment and allows a method to be chosen to interpret or render the data. Includes mime type parameters such as charset where appropriate.</t>
+  </si>
+  <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
+  </si>
+  <si>
+    <t>Processors of the data need to be able to know how to interpret the data.</t>
+  </si>
+  <si>
+    <t>text/plain; charset=UTF-8, image/png</t>
+  </si>
+  <si>
+    <t>The mime type of an attachment. Any valid mime type is allowed.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/mimetypes|4.0.1</t>
+  </si>
+  <si>
+    <t>Attachment.contentType</t>
+  </si>
+  <si>
+    <t>./mediaType, ./charset</t>
+  </si>
+  <si>
+    <t>ED.2+ED.3/RP.2+RP.3. Note conversion may be needed if old style values are being used</t>
+  </si>
+  <si>
+    <t>DocumentReference.content.attachment.language</t>
+  </si>
+  <si>
+    <t>Human language of the content (BCP-47)</t>
+  </si>
+  <si>
+    <t>The human language of the content. The value can be any valid value according to BCP 47.</t>
+  </si>
+  <si>
+    <t>Users need to be able to choose between the languages in a set of attachments.</t>
+  </si>
+  <si>
+    <t>en-AU</t>
+  </si>
+  <si>
+    <t>Attachment.language</t>
+  </si>
+  <si>
+    <t>./language</t>
+  </si>
+  <si>
+    <t>DocumentReference.content.attachment.data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">base64Binary
+</t>
+  </si>
+  <si>
+    <t>Le document CDA est contenu dans l'élément .data au format base64.</t>
+  </si>
+  <si>
+    <t>The actual data of the attachment - a sequence of bytes, base64 encoded.</t>
+  </si>
+  <si>
+    <t>The base64-encoded data SHALL be expressed in the same character set as the base resource XML or JSON.</t>
+  </si>
+  <si>
+    <t>The data needs to able to be transmitted inline.</t>
+  </si>
+  <si>
+    <t>Attachment.data</t>
+  </si>
+  <si>
+    <t>./data</t>
+  </si>
+  <si>
+    <t>ED.5</t>
+  </si>
+  <si>
+    <t>DocumentReference.content.attachment.url</t>
+  </si>
+  <si>
+    <t xml:space="preserve">url
+</t>
+  </si>
+  <si>
+    <t>Uri where the data can be found</t>
+  </si>
+  <si>
+    <t>A location where the data can be accessed.</t>
+  </si>
+  <si>
+    <t>If both data and url are provided, the url SHALL point to the same content as the data contains. Urls may be relative references or may reference transient locations such as a wrapping envelope using cid: though this has ramifications for using signatures. Relative URLs are interpreted relative to the service url, like a resource reference, rather than relative to the resource itself. If a URL is provided, it SHALL resolve to actual data.</t>
+  </si>
+  <si>
+    <t>The data needs to be transmitted by reference.</t>
+  </si>
+  <si>
+    <t>http://www.acme.com/logo-small.png</t>
+  </si>
+  <si>
+    <t>Attachment.url</t>
+  </si>
+  <si>
+    <t>./reference/literal</t>
+  </si>
+  <si>
+    <t>RP.1+RP.2 - if they refer to a URL (see v2.6)</t>
+  </si>
+  <si>
+    <t>DocumentReference.content.attachment.size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unsignedInt
+</t>
+  </si>
+  <si>
+    <t>Number of bytes of content (if url provided)</t>
+  </si>
+  <si>
+    <t>The number of bytes of data that make up this attachment (before base64 encoding, if that is done).</t>
+  </si>
+  <si>
+    <t>The number of bytes is redundant if the data is provided as a base64binary, but is useful if the data is provided as a url reference.</t>
+  </si>
+  <si>
+    <t>Representing the size allows applications to determine whether they should fetch the content automatically in advance, or refuse to fetch it at all.</t>
+  </si>
+  <si>
+    <t>Attachment.size</t>
+  </si>
+  <si>
+    <t>N/A (needs data type R3 proposal)</t>
+  </si>
+  <si>
+    <t>DocumentReference.content.attachment.hash</t>
+  </si>
+  <si>
+    <t>Hash of the data (sha-1, base64ed)</t>
+  </si>
+  <si>
+    <t>The calculated hash of the data using SHA-1. Represented using base64.</t>
+  </si>
+  <si>
+    <t>The hash is calculated on the data prior to base64 encoding, if the data is based64 encoded. The hash is not intended to support digital signatures. Where protection against malicious threats a digital signature should be considered, see [Provenance.signature](http://hl7.org/fhir/R4/provenance-definitions.html#Provenance.signature) for mechanism to protect a resource with a digital signature.</t>
+  </si>
+  <si>
+    <t>Included so that applications can verify that the contents of a location have not changed due to technical failures (e.g., storage rot, transport glitch, incorrect version).</t>
+  </si>
+  <si>
+    <t>Attachment.hash</t>
+  </si>
+  <si>
+    <t>.integrityCheck[parent::ED/integrityCheckAlgorithm="SHA-1"]</t>
+  </si>
+  <si>
+    <t>DocumentReference.content.attachment.title</t>
+  </si>
+  <si>
+    <t>Label to display in place of the data</t>
+  </si>
+  <si>
+    <t>A label or set of text to display in place of the data.</t>
+  </si>
+  <si>
+    <t>Applications need a label to display to a human user in place of the actual data if the data cannot be rendered or perceived by the viewer.</t>
+  </si>
+  <si>
+    <t>Official Corporate Logo</t>
+  </si>
+  <si>
+    <t>Attachment.title</t>
+  </si>
+  <si>
+    <t>./title/data</t>
+  </si>
+  <si>
+    <t>DocumentReference.content.attachment.creation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Date attachment was first created</t>
+  </si>
+  <si>
+    <t>The date that the attachment was first created.</t>
+  </si>
+  <si>
+    <t>This is often tracked as an integrity issue for use of the attachment.</t>
+  </si>
+  <si>
+    <t>Attachment.creation</t>
   </si>
   <si>
     <t>DocumentReference.content.format</t>
@@ -1340,6 +1548,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -1503,15 +1726,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AQ45"/>
+  <dimension ref="A1:AQ55"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="46.23828125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="46.23828125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="50.828125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="50.828125" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="6" max="6" width="2.2109375" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="2.2109375" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="1.04296875" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="2.1640625" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="2.1640625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="77.93359375" customWidth="true" bestFit="true"/>
@@ -1522,7 +1745,7 @@
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="1.04296875" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="35.69140625" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="1.04296875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="1.04296875" customWidth="true" bestFit="true"/>
@@ -1672,7 +1895,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>46</v>
       </c>
@@ -1795,7 +2018,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>54</v>
       </c>
@@ -1916,7 +2139,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>62</v>
       </c>
@@ -2039,7 +2262,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>69</v>
       </c>
@@ -2162,7 +2385,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>78</v>
       </c>
@@ -2285,7 +2508,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>86</v>
       </c>
@@ -2408,7 +2631,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>93</v>
       </c>
@@ -2531,7 +2754,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>104</v>
       </c>
@@ -2656,7 +2879,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>109</v>
       </c>
@@ -2781,7 +3004,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>122</v>
       </c>
@@ -2902,7 +3125,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
         <v>128</v>
       </c>
@@ -3025,7 +3248,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
         <v>140</v>
       </c>
@@ -3148,7 +3371,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
         <v>149</v>
       </c>
@@ -3271,7 +3494,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
         <v>163</v>
       </c>
@@ -3394,7 +3617,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
         <v>176</v>
       </c>
@@ -3517,7 +3740,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
         <v>189</v>
       </c>
@@ -3640,7 +3863,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
         <v>199</v>
       </c>
@@ -3763,7 +3986,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
         <v>210</v>
       </c>
@@ -3886,7 +4109,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
         <v>221</v>
       </c>
@@ -4009,7 +4232,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
         <v>228</v>
       </c>
@@ -4132,7 +4355,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
         <v>236</v>
       </c>
@@ -4253,7 +4476,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
         <v>241</v>
       </c>
@@ -4376,7 +4599,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
         <v>244</v>
       </c>
@@ -4501,7 +4724,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
         <v>249</v>
       </c>
@@ -4624,7 +4847,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
         <v>258</v>
       </c>
@@ -4747,7 +4970,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
         <v>265</v>
       </c>
@@ -4872,7 +5095,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
         <v>273</v>
       </c>
@@ -4997,7 +5220,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
         <v>286</v>
       </c>
@@ -5016,7 +5239,7 @@
         <v>47</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>34</v>
@@ -5118,7 +5341,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
         <v>291</v>
       </c>
@@ -5239,7 +5462,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
         <v>292</v>
       </c>
@@ -5362,7 +5585,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
         <v>293</v>
       </c>
@@ -5487,7 +5710,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
         <v>294</v>
       </c>
@@ -5610,7 +5833,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
         <v>304</v>
       </c>
@@ -5635,20 +5858,18 @@
         <v>34</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>305</v>
+        <v>237</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>306</v>
+        <v>238</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>308</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>34</v>
@@ -5673,13 +5894,13 @@
         <v>34</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>309</v>
+        <v>34</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>310</v>
+        <v>34</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>34</v>
@@ -5697,7 +5918,7 @@
         <v>34</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>304</v>
+        <v>240</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>35</v>
@@ -5706,50 +5927,50 @@
         <v>47</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>311</v>
+        <v>34</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>290</v>
+        <v>68</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>312</v>
+        <v>34</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>313</v>
+        <v>34</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>314</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>34</v>
+        <v>94</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>35</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>34</v>
@@ -5758,19 +5979,19 @@
         <v>34</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>229</v>
+        <v>95</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>316</v>
+        <v>96</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>317</v>
+        <v>242</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>318</v>
+        <v>98</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5808,31 +6029,31 @@
         <v>34</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>34</v>
+        <v>99</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>34</v>
+        <v>101</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>315</v>
+        <v>243</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>59</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>60</v>
+        <v>103</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>34</v>
@@ -5841,7 +6062,7 @@
         <v>34</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>319</v>
+        <v>61</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>34</v>
@@ -5856,12 +6077,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>320</v>
+        <v>306</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>320</v>
+        <v>306</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5881,19 +6102,23 @@
         <v>34</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>237</v>
+        <v>70</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>238</v>
+        <v>307</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+        <v>308</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>34</v>
       </c>
@@ -5905,7 +6130,7 @@
         <v>34</v>
       </c>
       <c r="T36" t="s" s="2">
-        <v>34</v>
+        <v>311</v>
       </c>
       <c r="U36" t="s" s="2">
         <v>34</v>
@@ -5917,13 +6142,13 @@
         <v>34</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>34</v>
+        <v>132</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>34</v>
+        <v>312</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>34</v>
+        <v>313</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>34</v>
@@ -5941,7 +6166,7 @@
         <v>34</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>240</v>
+        <v>314</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>35</v>
@@ -5950,10 +6175,10 @@
         <v>47</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>34</v>
@@ -5962,7 +6187,7 @@
         <v>34</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>68</v>
+        <v>315</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>34</v>
@@ -5971,29 +6196,29 @@
         <v>34</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>34</v>
+        <v>316</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>34</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>94</v>
+        <v>34</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>35</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>34</v>
@@ -6002,21 +6227,23 @@
         <v>34</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>96</v>
+        <v>318</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>242</v>
+        <v>319</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="O37" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>320</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>34</v>
       </c>
@@ -6028,7 +6255,7 @@
         <v>34</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>34</v>
+        <v>321</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>34</v>
@@ -6040,43 +6267,43 @@
         <v>34</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>34</v>
+        <v>76</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>99</v>
+        <v>34</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>100</v>
+        <v>34</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>243</v>
+        <v>322</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>59</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>103</v>
+        <v>60</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>34</v>
@@ -6085,7 +6312,7 @@
         <v>34</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>61</v>
+        <v>323</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>34</v>
@@ -6100,47 +6327,47 @@
         <v>34</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>245</v>
+        <v>34</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>34</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>95</v>
+        <v>325</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>246</v>
+        <v>326</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>247</v>
+        <v>327</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>98</v>
+        <v>328</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>107</v>
+        <v>329</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>34</v>
@@ -6189,19 +6416,19 @@
         <v>34</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>248</v>
+        <v>330</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>59</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>103</v>
+        <v>60</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>34</v>
@@ -6210,7 +6437,7 @@
         <v>34</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>61</v>
+        <v>331</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>34</v>
@@ -6219,18 +6446,18 @@
         <v>34</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>34</v>
+        <v>332</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>34</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6241,7 +6468,7 @@
         <v>35</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>34</v>
@@ -6250,21 +6477,23 @@
         <v>34</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="O39" s="2"/>
+        <v>337</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>338</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>34</v>
       </c>
@@ -6276,7 +6505,7 @@
         <v>34</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>34</v>
+        <v>339</v>
       </c>
       <c r="U39" t="s" s="2">
         <v>34</v>
@@ -6312,48 +6541,48 @@
         <v>34</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>323</v>
+        <v>340</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>59</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>181</v>
+        <v>60</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>327</v>
+        <v>34</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>328</v>
+        <v>34</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>330</v>
+        <v>34</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>34</v>
+        <v>342</v>
       </c>
       <c r="AQ39" t="s" s="2">
         <v>34</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6364,7 +6593,7 @@
         <v>35</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>34</v>
@@ -6373,21 +6602,23 @@
         <v>34</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>150</v>
+        <v>344</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>332</v>
+        <v>345</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="O40" s="2"/>
+        <v>347</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>34</v>
       </c>
@@ -6411,13 +6642,13 @@
         <v>34</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>168</v>
+        <v>34</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>335</v>
+        <v>34</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>336</v>
+        <v>34</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>34</v>
@@ -6435,13 +6666,13 @@
         <v>34</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>331</v>
+        <v>349</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>59</v>
@@ -6453,10 +6684,10 @@
         <v>34</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>337</v>
+        <v>34</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>34</v>
@@ -6465,18 +6696,18 @@
         <v>34</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>174</v>
+        <v>34</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>339</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6499,18 +6730,20 @@
         <v>48</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>341</v>
+        <v>325</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>354</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>355</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>34</v>
       </c>
@@ -6558,7 +6791,7 @@
         <v>34</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>35</v>
@@ -6570,36 +6803,36 @@
         <v>59</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>345</v>
+        <v>60</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>346</v>
+        <v>34</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>348</v>
+        <v>34</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>349</v>
+        <v>34</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>350</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6619,21 +6852,23 @@
         <v>34</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>150</v>
+        <v>237</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="O42" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>361</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>34</v>
       </c>
@@ -6645,7 +6880,7 @@
         <v>34</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>34</v>
+        <v>362</v>
       </c>
       <c r="U42" t="s" s="2">
         <v>34</v>
@@ -6657,13 +6892,13 @@
         <v>34</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>168</v>
+        <v>34</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>355</v>
+        <v>34</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>356</v>
+        <v>34</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>34</v>
@@ -6681,7 +6916,7 @@
         <v>34</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>35</v>
@@ -6699,30 +6934,30 @@
         <v>34</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>357</v>
+        <v>34</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>359</v>
+        <v>34</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>174</v>
+        <v>34</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>360</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6742,22 +6977,20 @@
         <v>34</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>150</v>
+        <v>366</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>364</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>34</v>
@@ -6782,13 +7015,13 @@
         <v>34</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>168</v>
+        <v>34</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>366</v>
+        <v>34</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>367</v>
+        <v>34</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>34</v>
@@ -6806,7 +7039,7 @@
         <v>34</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>35</v>
@@ -6824,30 +7057,30 @@
         <v>34</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>357</v>
+        <v>34</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>357</v>
+        <v>34</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>174</v>
+        <v>34</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>368</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6867,19 +7100,19 @@
         <v>34</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>180</v>
+        <v>375</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6905,13 +7138,13 @@
         <v>34</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>34</v>
+        <v>376</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>34</v>
+        <v>377</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>34</v>
@@ -6929,7 +7162,7 @@
         <v>34</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>35</v>
@@ -6941,36 +7174,36 @@
         <v>59</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>181</v>
+        <v>60</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>183</v>
+        <v>378</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>184</v>
+        <v>290</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>185</v>
+        <v>379</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>34</v>
+        <v>380</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>373</v>
+        <v>381</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6981,7 +7214,7 @@
         <v>35</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>34</v>
@@ -6990,19 +7223,19 @@
         <v>34</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>375</v>
+        <v>229</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7052,43 +7285,1293 @@
         <v>34</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>59</v>
       </c>
       <c r="AJ45" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AO45" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AP45" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AQ45" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="46" hidden="true">
+      <c r="A46" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
+      <c r="P46" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AO46" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AP46" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AQ46" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="47" hidden="true">
+      <c r="A47" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="O47" s="2"/>
+      <c r="P47" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AO47" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AP47" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AQ47" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="48" hidden="true">
+      <c r="A48" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="P48" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="Q48" s="2"/>
+      <c r="R48" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AO48" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AP48" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AQ48" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="49" hidden="true">
+      <c r="A49" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="O49" s="2"/>
+      <c r="P49" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="Q49" s="2"/>
+      <c r="R49" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="AK45" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="AO45" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="AP45" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="AQ45" t="s" s="2">
-        <v>382</v>
+      <c r="AK49" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AO49" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="AP49" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AQ49" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="50" hidden="true">
+      <c r="A50" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="O50" s="2"/>
+      <c r="P50" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AO50" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AP50" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AQ50" t="s" s="2">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="51" hidden="true">
+      <c r="A51" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="O51" s="2"/>
+      <c r="P51" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AO51" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AP51" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AQ51" t="s" s="2">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="52" hidden="true">
+      <c r="A52" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="O52" s="2"/>
+      <c r="P52" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AO52" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AP52" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AQ52" t="s" s="2">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="53" hidden="true">
+      <c r="A53" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="P53" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AO53" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AP53" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AQ53" t="s" s="2">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="54" hidden="true">
+      <c r="A54" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="O54" s="2"/>
+      <c r="P54" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="AO54" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AP54" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AQ54" t="s" s="2">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="55" hidden="true">
+      <c r="A55" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="O55" s="2"/>
+      <c r="P55" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AO55" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AP55" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AQ55" t="s" s="2">
+        <v>449</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AQ55">
+    <filterColumn colId="6">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="26">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI54">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/ig/specifications_techniques/StructureDefinition-dui-documentreference.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-dui-documentreference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-13T08:02:35+00:00</t>
+    <t>2023-09-13T10:23:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-dui-documentreference.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-dui-documentreference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-13T10:23:45+00:00</t>
+    <t>2023-09-13T10:41:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-dui-documentreference.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-dui-documentreference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-13T10:41:32+00:00</t>
+    <t>2023-09-13T13:19:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-dui-documentreference.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-dui-documentreference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-13T13:19:45+00:00</t>
+    <t>2023-09-13T14:55:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-dui-documentreference.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-dui-documentreference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-13T14:55:53+00:00</t>
+    <t>2023-09-14T12:40:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-dui-documentreference.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-dui-documentreference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-14T12:40:46+00:00</t>
+    <t>2023-09-14T13:51:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-dui-documentreference.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-dui-documentreference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-14T13:51:30+00:00</t>
+    <t>2023-09-15T08:58:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-dui-documentreference.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-dui-documentreference.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2494" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2492" uniqueCount="488">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-18T08:18:21+00:00</t>
+    <t>2023-09-18T14:13:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -504,14 +504,10 @@
     <t>DocumentReference.modifierExtension</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -938,6 +934,9 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+  </si>
+  <si>
     <t>BackboneElement.modifierExtension</t>
   </si>
   <si>
@@ -1055,7 +1054,7 @@
     <t>Document contenu.</t>
   </si>
   <si>
-    <t>The document and format referenced. There may be multiple content element repetitions, each with a different format.</t>
+    <t>The document and format referenced.</t>
   </si>
   <si>
     <t>Bundle(Composition+*)</t>
@@ -3889,14 +3888,14 @@
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>35</v>
@@ -3916,12 +3915,8 @@
       <c r="M17" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="N17" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>157</v>
-      </c>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>35</v>
       </c>
@@ -3969,7 +3964,7 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>36</v>
@@ -3990,7 +3985,7 @@
         <v>35</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>35</v>
@@ -4007,10 +4002,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4018,7 +4013,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>48</v>
@@ -4033,19 +4028,19 @@
         <v>49</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="N18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>35</v>
@@ -4094,7 +4089,7 @@
         <v>35</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>36</v>
@@ -4109,33 +4104,33 @@
         <v>61</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AL18" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="AL18" t="s" s="2">
+      <c r="AM18" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="AM18" t="s" s="2">
+      <c r="AN18" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="AN18" t="s" s="2">
+      <c r="AO18" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="AO18" t="s" s="2">
+      <c r="AP18" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="AP18" t="s" s="2">
+      <c r="AQ18" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="AQ18" t="s" s="2">
-        <v>171</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4146,7 +4141,7 @@
         <v>36</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>49</v>
@@ -4158,13 +4153,13 @@
         <v>49</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4215,7 +4210,7 @@
         <v>35</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>36</v>
@@ -4230,33 +4225,33 @@
         <v>61</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AM19" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AN19" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AO19" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AP19" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="AN19" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="AP19" t="s" s="2">
+      <c r="AQ19" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="AQ19" t="s" s="2">
-        <v>177</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4282,13 +4277,13 @@
         <v>128</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>180</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>181</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4299,29 +4294,29 @@
         <v>35</v>
       </c>
       <c r="S20" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="T20" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="U20" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="V20" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="W20" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="X20" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="T20" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="U20" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="V20" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="W20" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="X20" t="s" s="2">
+      <c r="Y20" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="Y20" t="s" s="2">
+      <c r="Z20" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="Z20" t="s" s="2">
-        <v>185</v>
-      </c>
       <c r="AA20" t="s" s="2">
         <v>35</v>
       </c>
@@ -4338,7 +4333,7 @@
         <v>35</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>48</v>
@@ -4353,33 +4348,33 @@
         <v>61</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="AL20" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AM20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AO20" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="AN20" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AO20" t="s" s="2">
+      <c r="AP20" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="AP20" t="s" s="2">
+      <c r="AQ20" t="s" s="2">
         <v>189</v>
-      </c>
-      <c r="AQ20" t="s" s="2">
-        <v>190</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4390,7 +4385,7 @@
         <v>36</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>35</v>
@@ -4405,13 +4400,13 @@
         <v>128</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>194</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4437,14 +4432,14 @@
         <v>35</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Y21" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="Z21" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="Z21" t="s" s="2">
-        <v>196</v>
-      </c>
       <c r="AA21" t="s" s="2">
         <v>35</v>
       </c>
@@ -4461,7 +4456,7 @@
         <v>35</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>36</v>
@@ -4479,19 +4474,19 @@
         <v>35</v>
       </c>
       <c r="AL21" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="AM21" t="s" s="2">
+      <c r="AN21" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AO21" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AP21" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="AP21" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AQ21" t="s" s="2">
         <v>35</v>
@@ -4499,10 +4494,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4525,16 +4520,16 @@
         <v>49</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4564,7 +4559,7 @@
       </c>
       <c r="Y22" s="2"/>
       <c r="Z22" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>35</v>
@@ -4582,7 +4577,7 @@
         <v>35</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>36</v>
@@ -4594,47 +4589,47 @@
         <v>60</v>
       </c>
       <c r="AJ22" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="AK22" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="AK22" t="s" s="2">
+      <c r="AL22" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="AL22" t="s" s="2">
+      <c r="AM22" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="AM22" t="s" s="2">
+      <c r="AN22" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="AN22" t="s" s="2">
+      <c r="AO22" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="AO22" t="s" s="2">
+      <c r="AP22" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="AP22" t="s" s="2">
+      <c r="AQ22" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="AQ22" t="s" s="2">
-        <v>213</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>36</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>49</v>
@@ -4646,16 +4641,16 @@
         <v>49</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4685,7 +4680,7 @@
       </c>
       <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>35</v>
@@ -4703,7 +4698,7 @@
         <v>35</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>36</v>
@@ -4715,36 +4710,36 @@
         <v>60</v>
       </c>
       <c r="AJ23" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="AK23" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AL23" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="AK23" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AL23" t="s" s="2">
+      <c r="AM23" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="AN23" t="s" s="2">
+      <c r="AO23" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AP23" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="AO23" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="AP23" t="s" s="2">
+      <c r="AQ23" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="AQ23" t="s" s="2">
-        <v>225</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4767,16 +4762,16 @@
         <v>49</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>227</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4826,7 +4821,7 @@
         <v>35</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>36</v>
@@ -4838,40 +4833,40 @@
         <v>60</v>
       </c>
       <c r="AJ24" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="AK24" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="AK24" t="s" s="2">
+      <c r="AL24" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="AL24" t="s" s="2">
+      <c r="AM24" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AN24" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="AN24" t="s" s="2">
+      <c r="AO24" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="AO24" t="s" s="2">
+      <c r="AP24" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="AP24" t="s" s="2">
+      <c r="AQ24" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="AQ24" t="s" s="2">
-        <v>238</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4893,13 +4888,13 @@
         <v>86</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4949,7 +4944,7 @@
         <v>35</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>36</v>
@@ -4964,19 +4959,19 @@
         <v>61</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AL25" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="AL25" t="s" s="2">
+      <c r="AM25" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AN25" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AO25" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>35</v>
@@ -4987,10 +4982,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5013,16 +5008,16 @@
         <v>49</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5072,7 +5067,7 @@
         <v>35</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>36</v>
@@ -5084,36 +5079,36 @@
         <v>60</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AL26" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="AL26" t="s" s="2">
+      <c r="AM26" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="AM26" t="s" s="2">
+      <c r="AN26" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="AN26" t="s" s="2">
+      <c r="AO26" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AP26" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="AO26" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AP26" t="s" s="2">
+      <c r="AQ26" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="AQ26" t="s" s="2">
-        <v>258</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5136,16 +5131,16 @@
         <v>35</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5195,7 +5190,7 @@
         <v>35</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>36</v>
@@ -5207,36 +5202,36 @@
         <v>60</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AL27" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AM27" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="AM27" t="s" s="2">
+      <c r="AN27" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="AN27" t="s" s="2">
+      <c r="AO27" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="AO27" t="s" s="2">
+      <c r="AP27" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="AP27" t="s" s="2">
+      <c r="AQ27" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="AQ27" t="s" s="2">
-        <v>269</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5259,16 +5254,16 @@
         <v>35</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5318,7 +5313,7 @@
         <v>35</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>36</v>
@@ -5330,16 +5325,16 @@
         <v>60</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AL28" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AM28" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>35</v>
@@ -5356,10 +5351,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5373,7 +5368,7 @@
         <v>37</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>35</v>
@@ -5382,16 +5377,16 @@
         <v>49</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5441,7 +5436,7 @@
         <v>35</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>36</v>
@@ -5459,30 +5454,30 @@
         <v>35</v>
       </c>
       <c r="AL29" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AM29" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="AM29" t="s" s="2">
+      <c r="AN29" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AO29" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AP29" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="AQ29" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AP29" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="AQ29" t="s" s="2">
-        <v>284</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5600,10 +5595,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5723,14 +5718,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5752,16 +5747,16 @@
         <v>71</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="N32" t="s" s="2">
         <v>74</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>157</v>
+        <v>290</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>35</v>
@@ -5909,7 +5904,7 @@
         <v>35</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Y33" t="s" s="2">
         <v>296</v>
@@ -6006,7 +6001,7 @@
         <v>304</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6068,7 +6063,7 @@
         <v>60</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>35</v>
@@ -6236,7 +6231,7 @@
         <v>37</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>35</v>
@@ -6245,7 +6240,7 @@
         <v>49</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L36" t="s" s="2">
         <v>317</v>
@@ -6358,7 +6353,7 @@
         <v>48</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>49</v>
@@ -6370,7 +6365,7 @@
         <v>49</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="L37" t="s" s="2">
         <v>328</v>
@@ -6716,7 +6711,7 @@
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6738,16 +6733,16 @@
         <v>71</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>157</v>
+        <v>290</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>35</v>
@@ -7264,7 +7259,7 @@
         <v>35</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Y44" t="s" s="2">
         <v>353</v>
@@ -8346,7 +8341,7 @@
         <v>49</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="L53" t="s" s="2">
         <v>422</v>
@@ -8694,7 +8689,7 @@
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8716,16 +8711,16 @@
         <v>71</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>74</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>157</v>
+        <v>290</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>35</v>
@@ -8847,7 +8842,7 @@
         <v>432</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8909,7 +8904,7 @@
         <v>60</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>433</v>
@@ -8961,7 +8956,7 @@
         <v>35</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L58" t="s" s="2">
         <v>438</v>
@@ -9050,7 +9045,7 @@
         <v>35</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>446</v>
@@ -9207,7 +9202,7 @@
         <v>35</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L60" t="s" s="2">
         <v>459</v>
@@ -9294,7 +9289,7 @@
         <v>35</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>467</v>
@@ -9328,7 +9323,7 @@
         <v>35</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L61" t="s" s="2">
         <v>469</v>
@@ -9417,7 +9412,7 @@
         <v>35</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>474</v>
@@ -9442,7 +9437,7 @@
         <v>48</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>35</v>
@@ -9451,7 +9446,7 @@
         <v>35</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L62" t="s" s="2">
         <v>476</v>
@@ -9460,7 +9455,7 @@
         <v>477</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9522,19 +9517,19 @@
         <v>60</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>35</v>
       </c>
       <c r="AL62" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="AM62" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="AM62" t="s" s="2">
+      <c r="AN62" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>35</v>
@@ -9645,7 +9640,7 @@
         <v>60</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>35</v>

--- a/ig/specifications_techniques/StructureDefinition-dui-documentreference.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-dui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-18T14:13:30+00:00</t>
+    <t>2023-09-18T16:20:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-dui-documentreference.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-dui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-18T16:20:24+00:00</t>
+    <t>2023-09-20T09:28:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/specifications_techniques/StructureDefinition-dui-documentreference.xlsx
+++ b/ig/specifications_techniques/StructureDefinition-dui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-20T09:28:33+00:00</t>
+    <t>2023-09-20T10:55:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
